--- a/7500 sijk.xlsx
+++ b/7500 sijk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerja\2025\SF2026\Matching SF dengan LKPP dan SIJK\SIJK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\projek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD0564E0-1B32-4136-AD0E-624CE13D020D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA8089D-9286-48CB-82C2-94B3C3ABC6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{F900F670-05FD-4116-AD8A-84D90AE13E0B}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{F900F670-05FD-4116-AD8A-84D90AE13E0B}"/>
   </bookViews>
   <sheets>
     <sheet name="75" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4319" uniqueCount="1242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4319" uniqueCount="1241">
   <si>
     <t>tgl_tarik</t>
   </si>
@@ -3568,9 +3568,6 @@
   </si>
   <si>
     <t>2025-10-02 03:08:54.942513</t>
-  </si>
-  <si>
-    <t>351728</t>
   </si>
   <si>
     <t>0032415614822000</t>
@@ -3775,12 +3772,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -3810,11 +3819,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4130,9 +4141,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEE262F-8601-4B77-8FA2-2969489AD121}">
   <dimension ref="A1:AK117"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="122.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="54.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="71.36328125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4245,7 +4294,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -4358,7 +4407,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -4471,7 +4520,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -4584,7 +4633,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>95</v>
       </c>
@@ -4697,7 +4746,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>108</v>
       </c>
@@ -4810,120 +4859,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="M7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="S7" t="s">
+      <c r="S7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U7" t="s">
+      <c r="U7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V7" t="s">
+      <c r="V7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Y7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Z7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB7" t="s">
+      <c r="Z7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AC7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AD7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AE7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH7" t="s">
+      <c r="AF7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AI7" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AK7" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>139</v>
       </c>
@@ -5036,346 +5085,346 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="M9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R9" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S9" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="U9" t="s">
+      <c r="U9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="V9" t="s">
+      <c r="V9" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="W9" t="s">
+      <c r="W9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="Y9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB9" t="s">
+      <c r="Z9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AC9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AD9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AE9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AF9" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH9" t="s">
+      <c r="AF9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH9" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AI9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AK9" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="M10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S10" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U10" t="s">
+      <c r="U10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V10" t="s">
+      <c r="V10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="W10" t="s">
+      <c r="W10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X10" t="s">
+      <c r="X10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="Y10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB10" t="s">
+      <c r="Z10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AC10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AD10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AE10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH10" t="s">
+      <c r="AF10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH10" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="AI10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AJ10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AK10" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="M11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="S11" t="s">
+      <c r="S11" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U11" t="s">
+      <c r="U11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V11" t="s">
+      <c r="V11" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="W11" t="s">
+      <c r="W11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X11" t="s">
+      <c r="X11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="Y11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB11" t="s">
+      <c r="Z11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AC11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AD11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AE11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH11" t="s">
+      <c r="AF11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH11" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AI11" t="s">
+      <c r="AI11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AJ11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AK11" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>185</v>
       </c>
@@ -5488,459 +5537,459 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="E13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M13" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="M13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="Q13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R13" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="S13" t="s">
+      <c r="S13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="T13" t="s">
+      <c r="T13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U13" t="s">
+      <c r="U13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V13" t="s">
+      <c r="V13" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="W13" t="s">
+      <c r="W13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X13" t="s">
+      <c r="X13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Y13" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="Z13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB13" t="s">
+      <c r="Z13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AC13" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AD13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AE13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF13" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH13" t="s">
+      <c r="AF13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH13" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AI13" t="s">
+      <c r="AI13" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AJ13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AK13" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M14" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="M14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="Q14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R14" t="s">
+      <c r="R14" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="S14" t="s">
+      <c r="S14" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="T14" t="s">
+      <c r="T14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U14" t="s">
+      <c r="U14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V14" t="s">
+      <c r="V14" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="W14" t="s">
+      <c r="W14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X14" t="s">
+      <c r="X14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Y14" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="Z14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="Z14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AC14" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AD14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AE14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF14" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH14" t="s">
+      <c r="AF14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH14" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="AI14" t="s">
+      <c r="AI14" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ14" t="s">
+      <c r="AJ14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AK14" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M15" t="s">
-        <v>41</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="M15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="Q15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R15" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S15" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T15" t="s">
+      <c r="T15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U15" t="s">
+      <c r="U15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V15" t="s">
+      <c r="V15" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="W15" t="s">
+      <c r="W15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X15" t="s">
+      <c r="X15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Y15" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="Z15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB15" t="s">
+      <c r="Z15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AC15" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AD15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE15" t="s">
+      <c r="AE15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH15" t="s">
+      <c r="AF15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH15" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="AI15" t="s">
+      <c r="AI15" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ15" t="s">
+      <c r="AJ15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AK15" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M16" t="s">
-        <v>41</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="M16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R16" t="s">
+      <c r="R16" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="S16" t="s">
+      <c r="S16" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="T16" t="s">
+      <c r="T16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U16" t="s">
+      <c r="U16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V16" t="s">
+      <c r="V16" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="W16" t="s">
+      <c r="W16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X16" t="s">
+      <c r="X16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Y16" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Z16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB16" t="s">
+      <c r="Z16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AC16" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AD16" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE16" t="s">
+      <c r="AE16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH16" t="s">
+      <c r="AF16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH16" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="AI16" t="s">
+      <c r="AI16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AJ16" t="s">
+      <c r="AJ16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK16" t="s">
+      <c r="AK16" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>235</v>
       </c>
@@ -6053,7 +6102,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>253</v>
       </c>
@@ -6166,7 +6215,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>264</v>
       </c>
@@ -6279,120 +6328,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M20" t="s">
-        <v>41</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="M20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O20" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R20" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S20" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U20" t="s">
+      <c r="U20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V20" t="s">
+      <c r="V20" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="W20" t="s">
+      <c r="W20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X20" t="s">
+      <c r="X20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="Y20" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="Z20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB20" t="s">
+      <c r="Z20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AC20" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AD20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE20" t="s">
+      <c r="AE20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH20" t="s">
+      <c r="AF20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH20" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AI20" t="s">
+      <c r="AI20" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ20" t="s">
+      <c r="AJ20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK20" t="s">
+      <c r="AK20" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>290</v>
       </c>
@@ -6505,7 +6554,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>305</v>
       </c>
@@ -6618,7 +6667,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>316</v>
       </c>
@@ -6731,7 +6780,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>325</v>
       </c>
@@ -6844,7 +6893,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>336</v>
       </c>
@@ -6957,7 +7006,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>347</v>
       </c>
@@ -7070,7 +7119,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>358</v>
       </c>
@@ -7183,7 +7232,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>369</v>
       </c>
@@ -7296,120 +7345,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E29" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M29" t="s">
-        <v>41</v>
-      </c>
-      <c r="N29" t="s">
+      <c r="M29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="O29" t="s">
+      <c r="O29" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="Q29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R29" t="s">
+      <c r="R29" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="S29" t="s">
+      <c r="S29" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="T29" t="s">
+      <c r="T29" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U29" t="s">
+      <c r="U29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V29" t="s">
+      <c r="V29" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="W29" t="s">
+      <c r="W29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X29" t="s">
+      <c r="X29" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Y29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z29" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB29" t="s">
+      <c r="Z29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AC29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AD29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE29" t="s">
+      <c r="AE29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF29" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH29" t="s">
+      <c r="AF29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH29" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="AI29" t="s">
+      <c r="AI29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ29" t="s">
+      <c r="AJ29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK29" t="s">
+      <c r="AK29" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>391</v>
       </c>
@@ -7522,7 +7571,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>391</v>
       </c>
@@ -7635,7 +7684,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>409</v>
       </c>
@@ -7748,7 +7797,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>418</v>
       </c>
@@ -7861,7 +7910,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>429</v>
       </c>
@@ -7974,7 +8023,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>442</v>
       </c>
@@ -8087,7 +8136,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>453</v>
       </c>
@@ -8200,7 +8249,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>464</v>
       </c>
@@ -8313,7 +8362,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>464</v>
       </c>
@@ -8426,233 +8475,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E39" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K39" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L39" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M39" t="s">
-        <v>41</v>
-      </c>
-      <c r="N39" t="s">
+      <c r="M39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N39" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O39" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P39" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="Q39" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R39" t="s">
+      <c r="R39" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="S39" t="s">
+      <c r="S39" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="T39" t="s">
+      <c r="T39" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U39" t="s">
+      <c r="U39" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V39" t="s">
+      <c r="V39" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="W39" t="s">
+      <c r="W39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X39" t="s">
+      <c r="X39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Y39" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB39" t="s">
+      <c r="Z39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB39" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC39" t="s">
+      <c r="AC39" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD39" t="s">
+      <c r="AD39" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE39" t="s">
+      <c r="AE39" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH39" t="s">
+      <c r="AF39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH39" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="AI39" t="s">
+      <c r="AI39" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ39" t="s">
+      <c r="AJ39" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK39" t="s">
+      <c r="AK39" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="E40" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M40" t="s">
-        <v>41</v>
-      </c>
-      <c r="N40" t="s">
+      <c r="M40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="O40" t="s">
+      <c r="O40" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P40" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="Q40" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R40" t="s">
+      <c r="R40" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="S40" t="s">
+      <c r="S40" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="T40" t="s">
+      <c r="T40" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U40" t="s">
+      <c r="U40" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V40" t="s">
+      <c r="V40" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="W40" t="s">
+      <c r="W40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X40" t="s">
+      <c r="X40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Y40" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="Z40" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB40" t="s">
+      <c r="Z40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC40" t="s">
+      <c r="AC40" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AD40" t="s">
+      <c r="AD40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE40" t="s">
+      <c r="AE40" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF40" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH40" t="s">
+      <c r="AF40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH40" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="AI40" t="s">
+      <c r="AI40" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ40" t="s">
+      <c r="AJ40" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK40" t="s">
+      <c r="AK40" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>502</v>
       </c>
@@ -8765,120 +8814,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E42" t="s">
-        <v>41</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M42" t="s">
-        <v>41</v>
-      </c>
-      <c r="N42" t="s">
+      <c r="M42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N42" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="O42" t="s">
+      <c r="O42" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="Q42" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R42" t="s">
+      <c r="R42" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="S42" t="s">
+      <c r="S42" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="T42" t="s">
+      <c r="T42" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U42" t="s">
+      <c r="U42" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V42" t="s">
+      <c r="V42" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="W42" t="s">
+      <c r="W42" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X42" t="s">
+      <c r="X42" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="Y42" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB42" t="s">
+      <c r="Z42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AC42" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD42" t="s">
+      <c r="AD42" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE42" t="s">
+      <c r="AE42" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF42" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH42" t="s">
+      <c r="AF42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH42" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="AI42" t="s">
+      <c r="AI42" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ42" t="s">
+      <c r="AJ42" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK42" t="s">
+      <c r="AK42" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>525</v>
       </c>
@@ -8991,7 +9040,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>536</v>
       </c>
@@ -9104,7 +9153,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>536</v>
       </c>
@@ -9217,7 +9266,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>557</v>
       </c>
@@ -9330,7 +9379,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>568</v>
       </c>
@@ -9443,7 +9492,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>579</v>
       </c>
@@ -9556,7 +9605,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>590</v>
       </c>
@@ -9669,7 +9718,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>590</v>
       </c>
@@ -9782,7 +9831,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>606</v>
       </c>
@@ -9895,7 +9944,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>617</v>
       </c>
@@ -10008,7 +10057,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>628</v>
       </c>
@@ -10121,7 +10170,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>628</v>
       </c>
@@ -10234,7 +10283,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>649</v>
       </c>
@@ -10347,7 +10396,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>660</v>
       </c>
@@ -10460,233 +10509,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L57" t="s">
+      <c r="L57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M57" t="s">
-        <v>41</v>
-      </c>
-      <c r="N57" t="s">
+      <c r="M57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N57" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="O57" t="s">
+      <c r="O57" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="P57" t="s">
+      <c r="P57" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="Q57" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R57" t="s">
+      <c r="R57" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="S57" t="s">
+      <c r="S57" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="T57" t="s">
+      <c r="T57" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U57" t="s">
+      <c r="U57" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V57" t="s">
+      <c r="V57" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="W57" t="s">
+      <c r="W57" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X57" t="s">
+      <c r="X57" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y57" t="s">
+      <c r="Y57" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="Z57" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA57" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB57" t="s">
+      <c r="Z57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB57" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC57" t="s">
+      <c r="AC57" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AD57" t="s">
+      <c r="AD57" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE57" t="s">
+      <c r="AE57" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF57" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH57" t="s">
+      <c r="AF57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH57" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="AI57" t="s">
+      <c r="AI57" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AJ57" t="s">
+      <c r="AJ57" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK57" t="s">
+      <c r="AK57" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L58" t="s">
+      <c r="L58" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M58" t="s">
-        <v>41</v>
-      </c>
-      <c r="N58" t="s">
+      <c r="M58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N58" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="O58" t="s">
+      <c r="O58" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="P58" t="s">
+      <c r="P58" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="Q58" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R58" t="s">
+      <c r="R58" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="S58" t="s">
+      <c r="S58" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="T58" t="s">
+      <c r="T58" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U58" t="s">
+      <c r="U58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V58" t="s">
+      <c r="V58" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="W58" t="s">
+      <c r="W58" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X58" t="s">
+      <c r="X58" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y58" t="s">
+      <c r="Y58" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z58" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA58" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB58" t="s">
+      <c r="Z58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB58" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC58" t="s">
+      <c r="AC58" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD58" t="s">
+      <c r="AD58" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE58" t="s">
+      <c r="AE58" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF58" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG58" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH58" t="s">
+      <c r="AF58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH58" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="AI58" t="s">
+      <c r="AI58" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ58" t="s">
+      <c r="AJ58" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK58" t="s">
+      <c r="AK58" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>686</v>
       </c>
@@ -10799,7 +10848,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>699</v>
       </c>
@@ -10912,120 +10961,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="E61" t="s">
-        <v>41</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K61" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L61" t="s">
+      <c r="L61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M61" t="s">
-        <v>41</v>
-      </c>
-      <c r="N61" t="s">
+      <c r="M61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N61" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="O61" t="s">
+      <c r="O61" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="P61" t="s">
+      <c r="P61" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="Q61" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R61" t="s">
+      <c r="R61" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="S61" t="s">
+      <c r="S61" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="T61" t="s">
+      <c r="T61" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U61" t="s">
+      <c r="U61" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V61" t="s">
+      <c r="V61" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="W61" t="s">
+      <c r="W61" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X61" t="s">
+      <c r="X61" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="Y61" t="s">
+      <c r="Y61" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z61" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA61" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB61" t="s">
+      <c r="Z61" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA61" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC61" t="s">
+      <c r="AC61" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD61" t="s">
+      <c r="AD61" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE61" t="s">
+      <c r="AE61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF61" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH61" t="s">
+      <c r="AF61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH61" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="AI61" t="s">
+      <c r="AI61" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ61" t="s">
+      <c r="AJ61" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK61" t="s">
+      <c r="AK61" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>718</v>
       </c>
@@ -11138,7 +11187,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>729</v>
       </c>
@@ -11251,7 +11300,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>740</v>
       </c>
@@ -11364,120 +11413,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="E65" t="s">
-        <v>41</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K65" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L65" t="s">
+      <c r="L65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M65" t="s">
-        <v>41</v>
-      </c>
-      <c r="N65" t="s">
+      <c r="M65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N65" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O65" t="s">
+      <c r="O65" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P65" t="s">
+      <c r="P65" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="Q65" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R65" t="s">
+      <c r="R65" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="S65" t="s">
+      <c r="S65" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="T65" t="s">
+      <c r="T65" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U65" t="s">
+      <c r="U65" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V65" t="s">
+      <c r="V65" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="W65" t="s">
+      <c r="W65" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X65" t="s">
+      <c r="X65" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y65" t="s">
+      <c r="Y65" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="Z65" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB65" t="s">
+      <c r="Z65" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA65" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB65" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC65" t="s">
+      <c r="AC65" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AD65" t="s">
+      <c r="AD65" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AE65" t="s">
+      <c r="AE65" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF65" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG65" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH65" t="s">
+      <c r="AF65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH65" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="AI65" t="s">
+      <c r="AI65" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AJ65" t="s">
+      <c r="AJ65" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK65" t="s">
+      <c r="AK65" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>751</v>
       </c>
@@ -11590,346 +11639,346 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="E67" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="E67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K67" t="s">
+      <c r="K67" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L67" t="s">
+      <c r="L67" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M67" t="s">
-        <v>41</v>
-      </c>
-      <c r="N67" t="s">
+      <c r="M67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N67" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="O67" t="s">
+      <c r="O67" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="P67" t="s">
+      <c r="P67" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="Q67" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R67" t="s">
+      <c r="R67" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="S67" t="s">
+      <c r="S67" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="T67" t="s">
+      <c r="T67" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U67" t="s">
+      <c r="U67" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V67" t="s">
+      <c r="V67" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="W67" t="s">
+      <c r="W67" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X67" t="s">
+      <c r="X67" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y67" t="s">
+      <c r="Y67" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z67" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB67" t="s">
+      <c r="Z67" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA67" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB67" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC67" t="s">
+      <c r="AC67" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD67" t="s">
+      <c r="AD67" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE67" t="s">
+      <c r="AE67" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF67" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG67" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH67" t="s">
+      <c r="AF67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH67" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="AI67" t="s">
+      <c r="AI67" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ67" t="s">
+      <c r="AJ67" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK67" t="s">
+      <c r="AK67" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="E68" t="s">
-        <v>41</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="E68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I68" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K68" t="s">
+      <c r="K68" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L68" t="s">
+      <c r="L68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M68" t="s">
-        <v>41</v>
-      </c>
-      <c r="N68" t="s">
+      <c r="M68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N68" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="O68" t="s">
+      <c r="O68" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="P68" t="s">
+      <c r="P68" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="Q68" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R68" t="s">
+      <c r="R68" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="S68" t="s">
+      <c r="S68" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="T68" t="s">
+      <c r="T68" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U68" t="s">
+      <c r="U68" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V68" t="s">
+      <c r="V68" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="W68" t="s">
+      <c r="W68" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X68" t="s">
+      <c r="X68" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y68" t="s">
+      <c r="Y68" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z68" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB68" t="s">
+      <c r="Z68" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA68" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB68" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC68" t="s">
+      <c r="AC68" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD68" t="s">
+      <c r="AD68" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE68" t="s">
+      <c r="AE68" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF68" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG68" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH68" t="s">
+      <c r="AF68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH68" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="AI68" t="s">
+      <c r="AI68" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ68" t="s">
+      <c r="AJ68" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK68" t="s">
+      <c r="AK68" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E69" t="s">
-        <v>41</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="E69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L69" t="s">
+      <c r="L69" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M69" t="s">
-        <v>41</v>
-      </c>
-      <c r="N69" t="s">
+      <c r="M69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N69" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="O69" t="s">
+      <c r="O69" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="P69" t="s">
+      <c r="P69" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="Q69" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="R69" t="s">
+      <c r="R69" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="S69" t="s">
+      <c r="S69" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="T69" t="s">
+      <c r="T69" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="U69" t="s">
+      <c r="U69" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="V69" t="s">
+      <c r="V69" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="W69" t="s">
+      <c r="W69" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="X69" t="s">
+      <c r="X69" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Y69" t="s">
+      <c r="Y69" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="Z69" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB69" t="s">
+      <c r="Z69" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA69" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB69" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AC69" t="s">
+      <c r="AC69" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AD69" t="s">
+      <c r="AD69" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AE69" t="s">
+      <c r="AE69" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AF69" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH69" t="s">
+      <c r="AF69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH69" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="AI69" t="s">
+      <c r="AI69" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AJ69" t="s">
+      <c r="AJ69" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AK69" t="s">
+      <c r="AK69" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>798</v>
       </c>
@@ -12042,7 +12091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>798</v>
       </c>
@@ -12155,7 +12204,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>798</v>
       </c>
@@ -12268,7 +12317,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>822</v>
       </c>
@@ -12381,7 +12430,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>833</v>
       </c>
@@ -12494,7 +12543,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>833</v>
       </c>
@@ -12607,7 +12656,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>851</v>
       </c>
@@ -12720,7 +12769,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>851</v>
       </c>
@@ -12833,7 +12882,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>865</v>
       </c>
@@ -12946,7 +12995,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>876</v>
       </c>
@@ -13059,7 +13108,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>887</v>
       </c>
@@ -13172,7 +13221,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="81" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>898</v>
       </c>
@@ -13285,7 +13334,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>907</v>
       </c>
@@ -13398,233 +13447,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="83" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="83" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="E83" t="s">
-        <v>41</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E83" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="I83" t="s">
+      <c r="I83" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K83" t="s">
+      <c r="K83" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L83" t="s">
+      <c r="L83" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M83" t="s">
-        <v>41</v>
-      </c>
-      <c r="N83" t="s">
+      <c r="M83" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N83" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O83" t="s">
+      <c r="O83" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P83" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="Q83" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R83" t="s">
+      <c r="R83" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="S83" t="s">
+      <c r="S83" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="T83" t="s">
+      <c r="T83" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U83" t="s">
+      <c r="U83" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V83" t="s">
+      <c r="V83" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="W83" t="s">
+      <c r="W83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X83" t="s">
+      <c r="X83" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y83" t="s">
+      <c r="Y83" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z83" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA83" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB83" t="s">
+      <c r="Z83" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA83" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB83" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC83" t="s">
+      <c r="AC83" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD83" t="s">
+      <c r="AD83" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE83" t="s">
+      <c r="AE83" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF83" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG83" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH83" t="s">
+      <c r="AF83" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG83" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH83" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="AI83" t="s">
+      <c r="AI83" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ83" t="s">
+      <c r="AJ83" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK83" t="s">
+      <c r="AK83" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="84" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E84" t="s">
-        <v>41</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I84" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K84" t="s">
+      <c r="K84" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L84" t="s">
+      <c r="L84" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M84" t="s">
-        <v>41</v>
-      </c>
-      <c r="N84" t="s">
+      <c r="M84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N84" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O84" t="s">
+      <c r="O84" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P84" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q84" t="s">
+      <c r="Q84" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R84" t="s">
+      <c r="R84" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="S84" t="s">
+      <c r="S84" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="T84" t="s">
+      <c r="T84" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U84" t="s">
+      <c r="U84" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V84" t="s">
+      <c r="V84" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="W84" t="s">
+      <c r="W84" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X84" t="s">
+      <c r="X84" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y84" t="s">
+      <c r="Y84" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z84" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA84" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB84" t="s">
+      <c r="Z84" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA84" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB84" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC84" t="s">
+      <c r="AC84" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD84" t="s">
+      <c r="AD84" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE84" t="s">
+      <c r="AE84" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF84" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG84" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH84" t="s">
+      <c r="AF84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH84" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="AI84" t="s">
+      <c r="AI84" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ84" t="s">
+      <c r="AJ84" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK84" t="s">
+      <c r="AK84" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>929</v>
       </c>
@@ -13737,120 +13786,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="86" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="E86" t="s">
-        <v>41</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F86" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G86" s="3" t="s">
         <v>948</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I86" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="K86" t="s">
+      <c r="K86" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L86" t="s">
+      <c r="L86" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M86" t="s">
-        <v>41</v>
-      </c>
-      <c r="N86" t="s">
+      <c r="M86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N86" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="O86" t="s">
+      <c r="O86" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P86" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Q86" t="s">
+      <c r="Q86" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="R86" t="s">
+      <c r="R86" s="3" t="s">
         <v>950</v>
       </c>
-      <c r="S86" t="s">
+      <c r="S86" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="T86" t="s">
+      <c r="T86" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="U86" t="s">
+      <c r="U86" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="V86" t="s">
+      <c r="V86" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="W86" t="s">
+      <c r="W86" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="X86" t="s">
+      <c r="X86" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Y86" t="s">
+      <c r="Y86" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="Z86" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA86" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB86" t="s">
+      <c r="Z86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB86" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AC86" t="s">
+      <c r="AC86" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AD86" t="s">
+      <c r="AD86" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AE86" t="s">
+      <c r="AE86" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AF86" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG86" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH86" t="s">
+      <c r="AF86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH86" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="AI86" t="s">
+      <c r="AI86" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="AJ86" t="s">
+      <c r="AJ86" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AK86" t="s">
+      <c r="AK86" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="87" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>954</v>
       </c>
@@ -13948,7 +13997,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="88" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>954</v>
       </c>
@@ -14046,233 +14095,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="89" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="E89" t="s">
-        <v>41</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="E89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="I89" t="s">
+      <c r="I89" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K89" t="s">
+      <c r="K89" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L89" t="s">
+      <c r="L89" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M89" t="s">
-        <v>41</v>
-      </c>
-      <c r="N89" t="s">
+      <c r="M89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N89" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O89" t="s">
+      <c r="O89" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P89" t="s">
+      <c r="P89" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="Q89" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R89" t="s">
+      <c r="R89" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="S89" t="s">
+      <c r="S89" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="T89" t="s">
+      <c r="T89" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U89" t="s">
+      <c r="U89" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V89" t="s">
+      <c r="V89" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="W89" t="s">
+      <c r="W89" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X89" t="s">
+      <c r="X89" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y89" t="s">
+      <c r="Y89" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z89" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA89" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB89" t="s">
+      <c r="Z89" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA89" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB89" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC89" t="s">
+      <c r="AC89" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD89" t="s">
+      <c r="AD89" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE89" t="s">
+      <c r="AE89" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF89" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG89" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH89" t="s">
+      <c r="AF89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH89" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="AI89" t="s">
+      <c r="AI89" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ89" t="s">
+      <c r="AJ89" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK89" t="s">
+      <c r="AK89" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="90" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="90" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="E90" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="E90" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G90" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="I90" t="s">
+      <c r="I90" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J90" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="K90" t="s">
+      <c r="K90" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L90" t="s">
+      <c r="L90" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M90" t="s">
-        <v>41</v>
-      </c>
-      <c r="N90" t="s">
+      <c r="M90" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N90" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O90" t="s">
+      <c r="O90" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P90" t="s">
+      <c r="P90" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="Q90" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R90" t="s">
+      <c r="R90" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="S90" t="s">
+      <c r="S90" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="T90" t="s">
+      <c r="T90" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U90" t="s">
+      <c r="U90" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V90" t="s">
+      <c r="V90" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="W90" t="s">
+      <c r="W90" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X90" t="s">
+      <c r="X90" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y90" t="s">
+      <c r="Y90" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="Z90" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA90" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB90" t="s">
+      <c r="Z90" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA90" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB90" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC90" t="s">
+      <c r="AC90" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AD90" t="s">
+      <c r="AD90" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AE90" t="s">
+      <c r="AE90" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF90" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG90" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH90" t="s">
+      <c r="AF90" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG90" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH90" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="AI90" t="s">
+      <c r="AI90" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AJ90" t="s">
+      <c r="AJ90" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK90" t="s">
+      <c r="AK90" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>981</v>
       </c>
@@ -14385,7 +14434,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="92" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>994</v>
       </c>
@@ -14498,233 +14547,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="93" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="93" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="E93" t="s">
-        <v>41</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="E93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I93" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J93" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K93" t="s">
+      <c r="K93" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L93" t="s">
+      <c r="L93" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M93" t="s">
-        <v>41</v>
-      </c>
-      <c r="N93" t="s">
+      <c r="M93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="O93" t="s">
+      <c r="O93" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P93" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q93" t="s">
+      <c r="Q93" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R93" t="s">
+      <c r="R93" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="S93" t="s">
+      <c r="S93" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="T93" t="s">
+      <c r="T93" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U93" t="s">
+      <c r="U93" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V93" t="s">
+      <c r="V93" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="W93" t="s">
+      <c r="W93" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X93" t="s">
+      <c r="X93" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="Y93" t="s">
+      <c r="Y93" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Z93" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA93" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB93" t="s">
+      <c r="Z93" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA93" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB93" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC93" t="s">
+      <c r="AC93" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD93" t="s">
+      <c r="AD93" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE93" t="s">
+      <c r="AE93" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF93" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG93" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH93" t="s">
+      <c r="AF93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH93" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="AI93" t="s">
+      <c r="AI93" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AJ93" t="s">
+      <c r="AJ93" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK93" t="s">
+      <c r="AK93" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="94" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="94" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="E94" t="s">
-        <v>41</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="E94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G94" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I94" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J94" t="s">
+      <c r="J94" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K94" t="s">
+      <c r="K94" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L94" t="s">
+      <c r="L94" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M94" t="s">
-        <v>41</v>
-      </c>
-      <c r="N94" t="s">
+      <c r="M94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N94" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="O94" t="s">
+      <c r="O94" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="P94" t="s">
+      <c r="P94" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q94" t="s">
+      <c r="Q94" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R94" t="s">
+      <c r="R94" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="S94" t="s">
+      <c r="S94" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="T94" t="s">
+      <c r="T94" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U94" t="s">
+      <c r="U94" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V94" t="s">
+      <c r="V94" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="W94" t="s">
+      <c r="W94" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X94" t="s">
+      <c r="X94" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y94" t="s">
+      <c r="Y94" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z94" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA94" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB94" t="s">
+      <c r="Z94" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA94" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB94" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC94" t="s">
+      <c r="AC94" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD94" t="s">
+      <c r="AD94" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE94" t="s">
+      <c r="AE94" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF94" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG94" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH94" t="s">
+      <c r="AF94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH94" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="AI94" t="s">
+      <c r="AI94" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ94" t="s">
+      <c r="AJ94" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK94" t="s">
+      <c r="AK94" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>1027</v>
       </c>
@@ -14837,233 +14886,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="96" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="96" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="E96" t="s">
-        <v>41</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="E96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="G96" t="s">
+      <c r="G96" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="I96" t="s">
+      <c r="I96" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J96" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="K96" t="s">
+      <c r="K96" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L96" t="s">
+      <c r="L96" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M96" t="s">
-        <v>41</v>
-      </c>
-      <c r="N96" t="s">
+      <c r="M96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N96" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O96" t="s">
+      <c r="O96" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P96" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q96" t="s">
+      <c r="Q96" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R96" t="s">
+      <c r="R96" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="S96" t="s">
+      <c r="S96" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="T96" t="s">
+      <c r="T96" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U96" t="s">
+      <c r="U96" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V96" t="s">
+      <c r="V96" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="W96" t="s">
+      <c r="W96" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X96" t="s">
+      <c r="X96" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y96" t="s">
+      <c r="Y96" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="Z96" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA96" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB96" t="s">
+      <c r="Z96" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA96" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB96" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC96" t="s">
+      <c r="AC96" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AD96" t="s">
+      <c r="AD96" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AE96" t="s">
+      <c r="AE96" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF96" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG96" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH96" t="s">
+      <c r="AF96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH96" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="AI96" t="s">
+      <c r="AI96" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AJ96" t="s">
+      <c r="AJ96" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK96" t="s">
+      <c r="AK96" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="97" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="E97" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="E97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G97" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="I97" t="s">
+      <c r="I97" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J97" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K97" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L97" t="s">
+      <c r="L97" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M97" t="s">
-        <v>41</v>
-      </c>
-      <c r="N97" t="s">
+      <c r="M97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N97" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O97" t="s">
+      <c r="O97" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P97" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="Q97" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R97" t="s">
+      <c r="R97" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="S97" t="s">
+      <c r="S97" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="T97" t="s">
+      <c r="T97" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U97" t="s">
+      <c r="U97" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V97" t="s">
+      <c r="V97" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="W97" t="s">
+      <c r="W97" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X97" t="s">
+      <c r="X97" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y97" t="s">
+      <c r="Y97" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z97" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA97" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB97" t="s">
+      <c r="Z97" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA97" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB97" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC97" t="s">
+      <c r="AC97" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD97" t="s">
+      <c r="AD97" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE97" t="s">
+      <c r="AE97" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF97" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG97" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH97" t="s">
+      <c r="AF97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH97" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="AI97" t="s">
+      <c r="AI97" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ97" t="s">
+      <c r="AJ97" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK97" t="s">
+      <c r="AK97" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="98" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>1058</v>
       </c>
@@ -15176,7 +15225,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>1067</v>
       </c>
@@ -15289,7 +15338,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>1076</v>
       </c>
@@ -15402,120 +15451,120 @@
         <v>68</v>
       </c>
     </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+    <row r="101" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="E101" t="s">
-        <v>41</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="E101" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I101" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J101" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K101" t="s">
+      <c r="K101" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L101" t="s">
+      <c r="L101" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M101" t="s">
-        <v>41</v>
-      </c>
-      <c r="N101" t="s">
+      <c r="M101" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N101" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O101" t="s">
+      <c r="O101" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P101" t="s">
+      <c r="P101" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q101" t="s">
+      <c r="Q101" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R101" t="s">
+      <c r="R101" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="S101" t="s">
+      <c r="S101" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="T101" t="s">
+      <c r="T101" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U101" t="s">
+      <c r="U101" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V101" t="s">
+      <c r="V101" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="W101" t="s">
+      <c r="W101" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X101" t="s">
+      <c r="X101" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y101" t="s">
+      <c r="Y101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z101" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA101" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB101" t="s">
+      <c r="Z101" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA101" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB101" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC101" t="s">
+      <c r="AC101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD101" t="s">
+      <c r="AD101" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE101" t="s">
+      <c r="AE101" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF101" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG101" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH101" t="s">
+      <c r="AF101" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG101" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH101" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="AI101" t="s">
+      <c r="AI101" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ101" t="s">
+      <c r="AJ101" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK101" t="s">
+      <c r="AK101" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1087</v>
       </c>
@@ -15628,233 +15677,233 @@
         <v>68</v>
       </c>
     </row>
-    <row r="103" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+    <row r="103" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="E103" t="s">
-        <v>41</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="E103" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G103" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="I103" t="s">
+      <c r="I103" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J103" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K103" t="s">
+      <c r="K103" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L103" t="s">
+      <c r="L103" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M103" t="s">
-        <v>41</v>
-      </c>
-      <c r="N103" t="s">
+      <c r="M103" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N103" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="O103" t="s">
+      <c r="O103" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="P103" t="s">
+      <c r="P103" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q103" t="s">
+      <c r="Q103" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R103" t="s">
+      <c r="R103" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="S103" t="s">
+      <c r="S103" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="T103" t="s">
+      <c r="T103" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U103" t="s">
+      <c r="U103" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V103" t="s">
+      <c r="V103" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="W103" t="s">
+      <c r="W103" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X103" t="s">
+      <c r="X103" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y103" t="s">
+      <c r="Y103" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Z103" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA103" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB103" t="s">
+      <c r="Z103" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA103" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB103" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC103" t="s">
+      <c r="AC103" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD103" t="s">
+      <c r="AD103" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE103" t="s">
+      <c r="AE103" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF103" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG103" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH103" t="s">
+      <c r="AF103" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG103" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH103" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="AI103" t="s">
+      <c r="AI103" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AJ103" t="s">
+      <c r="AJ103" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK103" t="s">
+      <c r="AK103" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="104" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    <row r="104" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="E104" t="s">
-        <v>41</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="E104" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="I104" t="s">
+      <c r="I104" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J104" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K104" t="s">
+      <c r="K104" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L104" t="s">
+      <c r="L104" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M104" t="s">
-        <v>41</v>
-      </c>
-      <c r="N104" t="s">
+      <c r="M104" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N104" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O104" t="s">
+      <c r="O104" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P104" t="s">
+      <c r="P104" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q104" t="s">
+      <c r="Q104" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R104" t="s">
+      <c r="R104" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="S104" t="s">
+      <c r="S104" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="T104" t="s">
+      <c r="T104" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U104" t="s">
+      <c r="U104" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V104" t="s">
+      <c r="V104" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="W104" t="s">
+      <c r="W104" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X104" t="s">
+      <c r="X104" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y104" t="s">
+      <c r="Y104" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z104" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA104" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB104" t="s">
+      <c r="Z104" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA104" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB104" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC104" t="s">
+      <c r="AC104" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD104" t="s">
+      <c r="AD104" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE104" t="s">
+      <c r="AE104" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF104" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG104" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH104" t="s">
+      <c r="AF104" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG104" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH104" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="AI104" t="s">
+      <c r="AI104" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ104" t="s">
+      <c r="AJ104" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK104" t="s">
+      <c r="AK104" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="105" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>1121</v>
       </c>
@@ -15967,346 +16016,346 @@
         <v>68</v>
       </c>
     </row>
-    <row r="106" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+    <row r="106" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="E106" t="s">
-        <v>41</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="E106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G106" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="I106" t="s">
+      <c r="I106" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J106" t="s">
+      <c r="J106" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K106" t="s">
+      <c r="K106" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L106" t="s">
+      <c r="L106" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M106" t="s">
-        <v>41</v>
-      </c>
-      <c r="N106" t="s">
+      <c r="M106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N106" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="O106" t="s">
+      <c r="O106" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="P106" t="s">
+      <c r="P106" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q106" t="s">
+      <c r="Q106" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R106" t="s">
+      <c r="R106" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="S106" t="s">
+      <c r="S106" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="T106" t="s">
+      <c r="T106" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U106" t="s">
+      <c r="U106" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V106" t="s">
+      <c r="V106" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="W106" t="s">
+      <c r="W106" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X106" t="s">
+      <c r="X106" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y106" t="s">
+      <c r="Y106" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z106" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA106" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB106" t="s">
+      <c r="Z106" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA106" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB106" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC106" t="s">
+      <c r="AC106" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD106" t="s">
+      <c r="AD106" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE106" t="s">
+      <c r="AE106" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF106" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG106" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH106" t="s">
+      <c r="AF106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH106" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="AI106" t="s">
+      <c r="AI106" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ106" t="s">
+      <c r="AJ106" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK106" t="s">
+      <c r="AK106" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+    <row r="107" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="E107" t="s">
-        <v>41</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="E107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="I107" t="s">
+      <c r="I107" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J107" t="s">
+      <c r="J107" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="K107" t="s">
+      <c r="K107" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L107" t="s">
+      <c r="L107" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M107" t="s">
-        <v>41</v>
-      </c>
-      <c r="N107" t="s">
+      <c r="M107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N107" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="O107" t="s">
+      <c r="O107" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="P107" t="s">
+      <c r="P107" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q107" t="s">
+      <c r="Q107" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R107" t="s">
+      <c r="R107" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="S107" t="s">
+      <c r="S107" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="T107" t="s">
+      <c r="T107" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U107" t="s">
+      <c r="U107" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V107" t="s">
+      <c r="V107" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="W107" t="s">
+      <c r="W107" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X107" t="s">
+      <c r="X107" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y107" t="s">
+      <c r="Y107" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="Z107" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA107" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB107" t="s">
+      <c r="Z107" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA107" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB107" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC107" t="s">
+      <c r="AC107" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AD107" t="s">
+      <c r="AD107" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AE107" t="s">
+      <c r="AE107" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF107" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG107" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH107" t="s">
+      <c r="AF107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH107" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="AI107" t="s">
+      <c r="AI107" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AJ107" t="s">
+      <c r="AJ107" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK107" t="s">
+      <c r="AK107" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="108" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="E108" t="s">
-        <v>41</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="E108" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="I108" t="s">
+      <c r="I108" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J108" t="s">
+      <c r="J108" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K108" t="s">
+      <c r="K108" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L108" t="s">
+      <c r="L108" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M108" t="s">
-        <v>41</v>
-      </c>
-      <c r="N108" t="s">
+      <c r="M108" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N108" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="O108" t="s">
+      <c r="O108" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="P108" t="s">
+      <c r="P108" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q108" t="s">
+      <c r="Q108" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R108" t="s">
+      <c r="R108" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="S108" t="s">
+      <c r="S108" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="T108" t="s">
+      <c r="T108" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U108" t="s">
+      <c r="U108" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V108" t="s">
+      <c r="V108" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="W108" t="s">
+      <c r="W108" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X108" t="s">
+      <c r="X108" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y108" t="s">
+      <c r="Y108" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Z108" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA108" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB108" t="s">
+      <c r="Z108" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA108" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB108" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC108" t="s">
+      <c r="AC108" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD108" t="s">
+      <c r="AD108" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE108" t="s">
+      <c r="AE108" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF108" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG108" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH108" t="s">
+      <c r="AF108" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG108" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH108" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="AI108" t="s">
+      <c r="AI108" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AJ108" t="s">
+      <c r="AJ108" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK108" t="s">
+      <c r="AK108" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>1160</v>
       </c>
@@ -16419,143 +16468,143 @@
         <v>68</v>
       </c>
     </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+    <row r="110" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="G110" t="s">
+      <c r="G110" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="I110" t="s">
+      <c r="I110" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J110" t="s">
+      <c r="J110" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K110" t="s">
+      <c r="K110" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L110" t="s">
+      <c r="L110" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M110" t="s">
-        <v>41</v>
-      </c>
-      <c r="N110" t="s">
+      <c r="M110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N110" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="O110" t="s">
+      <c r="O110" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="P110" t="s">
+      <c r="P110" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q110" t="s">
+      <c r="Q110" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R110" t="s">
+      <c r="R110" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="S110" t="s">
+      <c r="S110" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="T110" t="s">
+      <c r="T110" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U110" t="s">
+      <c r="U110" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V110" t="s">
+      <c r="V110" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="W110" t="s">
+      <c r="W110" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X110" t="s">
+      <c r="X110" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y110" t="s">
+      <c r="Y110" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z110" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA110" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB110" t="s">
+      <c r="Z110" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA110" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB110" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC110" t="s">
+      <c r="AC110" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AD110" t="s">
+      <c r="AD110" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AE110" t="s">
+      <c r="AE110" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF110" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG110" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH110" t="s">
+      <c r="AF110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH110" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="AI110" t="s">
+      <c r="AI110" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ110" t="s">
+      <c r="AJ110" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK110" t="s">
+      <c r="AK110" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>1180</v>
       </c>
       <c r="B111" t="s">
+        <v>124</v>
+      </c>
+      <c r="C111" t="s">
         <v>1181</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>1182</v>
-      </c>
-      <c r="D111" t="s">
-        <v>1183</v>
       </c>
       <c r="E111" t="s">
         <v>891</v>
       </c>
       <c r="F111" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G111" t="s">
         <v>1184</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>1185</v>
-      </c>
-      <c r="H111" t="s">
-        <v>1186</v>
       </c>
       <c r="I111" t="s">
         <v>45</v>
@@ -16585,10 +16634,10 @@
         <v>52</v>
       </c>
       <c r="R111" t="s">
+        <v>1186</v>
+      </c>
+      <c r="S111" t="s">
         <v>1187</v>
-      </c>
-      <c r="S111" t="s">
-        <v>1188</v>
       </c>
       <c r="T111" t="s">
         <v>55</v>
@@ -16597,7 +16646,7 @@
         <v>56</v>
       </c>
       <c r="V111" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="W111" t="s">
         <v>58</v>
@@ -16633,7 +16682,7 @@
         <v>891</v>
       </c>
       <c r="AH111" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AI111" t="s">
         <v>81</v>
@@ -16645,30 +16694,30 @@
         <v>68</v>
       </c>
     </row>
-    <row r="112" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B112" t="s">
         <v>1191</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>1192</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>1193</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
+        <v>41</v>
+      </c>
+      <c r="F112" t="s">
         <v>1194</v>
       </c>
-      <c r="E112" t="s">
-        <v>41</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>1195</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>1196</v>
-      </c>
-      <c r="H112" t="s">
-        <v>1197</v>
       </c>
       <c r="I112" t="s">
         <v>45</v>
@@ -16710,7 +16759,7 @@
         <v>56</v>
       </c>
       <c r="V112" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="W112" t="s">
         <v>58</v>
@@ -16746,7 +16795,7 @@
         <v>41</v>
       </c>
       <c r="AH112" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="AI112" t="s">
         <v>81</v>
@@ -16758,369 +16807,369 @@
         <v>68</v>
       </c>
     </row>
-    <row r="113" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+    <row r="113" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="E113" t="s">
-        <v>506</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="G113" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R113" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="I113" t="s">
+      <c r="S113" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="T113" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U113" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y113" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z113" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA113" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB113" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC113" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD113" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE113" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF113" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG113" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH113" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AI113" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ113" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK113" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="I114" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J113" t="s">
-        <v>128</v>
-      </c>
-      <c r="K113" t="s">
+      <c r="J114" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="K114" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L113" t="s">
+      <c r="L114" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M113" t="s">
-        <v>41</v>
-      </c>
-      <c r="N113" t="s">
-        <v>129</v>
-      </c>
-      <c r="O113" t="s">
-        <v>130</v>
-      </c>
-      <c r="P113" t="s">
+      <c r="M114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="P114" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q113" t="s">
+      <c r="Q114" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R113" t="s">
-        <v>1207</v>
-      </c>
-      <c r="S113" t="s">
-        <v>1208</v>
-      </c>
-      <c r="T113" t="s">
+      <c r="R114" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="T114" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U113" t="s">
+      <c r="U114" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V113" t="s">
-        <v>1209</v>
-      </c>
-      <c r="W113" t="s">
+      <c r="V114" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="W114" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X113" t="s">
+      <c r="X114" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y113" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z113" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA113" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB113" t="s">
+      <c r="Y114" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z114" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA114" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB114" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC113" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD113" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE113" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF113" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG113" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH113" t="s">
-        <v>1210</v>
-      </c>
-      <c r="AI113" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ113" t="s">
+      <c r="AC114" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AD114" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AE114" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH114" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="AI114" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AJ114" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK113" t="s">
+      <c r="AK114" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="114" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C114" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D114" t="s">
-        <v>1214</v>
-      </c>
-      <c r="E114" t="s">
-        <v>41</v>
-      </c>
-      <c r="F114" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G114" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H114" t="s">
-        <v>894</v>
-      </c>
-      <c r="I114" t="s">
+    <row r="115" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I115" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J114" t="s">
-        <v>271</v>
-      </c>
-      <c r="K114" t="s">
+      <c r="J115" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K115" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L114" t="s">
+      <c r="L115" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M114" t="s">
-        <v>41</v>
-      </c>
-      <c r="N114" t="s">
-        <v>89</v>
-      </c>
-      <c r="O114" t="s">
-        <v>90</v>
-      </c>
-      <c r="P114" t="s">
+      <c r="M115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P115" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q114" t="s">
+      <c r="Q115" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R114" t="s">
-        <v>960</v>
-      </c>
-      <c r="S114" t="s">
-        <v>961</v>
-      </c>
-      <c r="T114" t="s">
+      <c r="R115" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="T115" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U114" t="s">
+      <c r="U115" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V114" t="s">
-        <v>1217</v>
-      </c>
-      <c r="W114" t="s">
+      <c r="V115" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="W115" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X114" t="s">
+      <c r="X115" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y114" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z114" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA114" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB114" t="s">
+      <c r="Y115" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z115" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA115" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB115" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC114" t="s">
-        <v>275</v>
-      </c>
-      <c r="AD114" t="s">
-        <v>276</v>
-      </c>
-      <c r="AE114" t="s">
+      <c r="AC115" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD115" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE115" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AF114" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG114" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH114" t="s">
+      <c r="AF115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH115" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="AI115" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ115" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK115" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>1218</v>
       </c>
-      <c r="AI114" t="s">
-        <v>278</v>
-      </c>
-      <c r="AJ114" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK114" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="115" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="B116" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D116" t="s">
         <v>1221</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E116" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" t="s">
         <v>1222</v>
       </c>
-      <c r="E115" t="s">
-        <v>41</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="G116" t="s">
         <v>1223</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H116" t="s">
         <v>1224</v>
-      </c>
-      <c r="H115" t="s">
-        <v>1225</v>
-      </c>
-      <c r="I115" t="s">
-        <v>45</v>
-      </c>
-      <c r="J115" t="s">
-        <v>46</v>
-      </c>
-      <c r="K115" t="s">
-        <v>47</v>
-      </c>
-      <c r="L115" t="s">
-        <v>48</v>
-      </c>
-      <c r="M115" t="s">
-        <v>41</v>
-      </c>
-      <c r="N115" t="s">
-        <v>102</v>
-      </c>
-      <c r="O115" t="s">
-        <v>103</v>
-      </c>
-      <c r="P115" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>52</v>
-      </c>
-      <c r="R115" t="s">
-        <v>1226</v>
-      </c>
-      <c r="S115" t="s">
-        <v>1227</v>
-      </c>
-      <c r="T115" t="s">
-        <v>55</v>
-      </c>
-      <c r="U115" t="s">
-        <v>56</v>
-      </c>
-      <c r="V115" t="s">
-        <v>1228</v>
-      </c>
-      <c r="W115" t="s">
-        <v>58</v>
-      </c>
-      <c r="X115" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y115" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA115" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB115" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC115" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD115" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE115" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF115" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG115" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH115" t="s">
-        <v>1229</v>
-      </c>
-      <c r="AI115" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ115" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK115" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="116" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D116" t="s">
-        <v>1222</v>
-      </c>
-      <c r="E116" t="s">
-        <v>41</v>
-      </c>
-      <c r="F116" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G116" t="s">
-        <v>1224</v>
-      </c>
-      <c r="H116" t="s">
-        <v>1225</v>
       </c>
       <c r="I116" t="s">
         <v>45</v>
@@ -17162,7 +17211,7 @@
         <v>56</v>
       </c>
       <c r="V116" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="W116" t="s">
         <v>58</v>
@@ -17198,7 +17247,7 @@
         <v>41</v>
       </c>
       <c r="AH116" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="AI116" t="s">
         <v>66</v>
@@ -17210,116 +17259,116 @@
         <v>68</v>
       </c>
     </row>
-    <row r="117" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+    <row r="117" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="E117" t="s">
-        <v>41</v>
-      </c>
-      <c r="F117" t="s">
+      <c r="G117" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N117" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="P117" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q117" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R117" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S117" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="T117" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U117" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V117" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="I117" t="s">
-        <v>45</v>
-      </c>
-      <c r="J117" t="s">
-        <v>46</v>
-      </c>
-      <c r="K117" t="s">
-        <v>47</v>
-      </c>
-      <c r="L117" t="s">
-        <v>48</v>
-      </c>
-      <c r="M117" t="s">
-        <v>41</v>
-      </c>
-      <c r="N117" t="s">
-        <v>398</v>
-      </c>
-      <c r="O117" t="s">
-        <v>399</v>
-      </c>
-      <c r="P117" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>52</v>
-      </c>
-      <c r="R117" t="s">
-        <v>343</v>
-      </c>
-      <c r="S117" t="s">
-        <v>344</v>
-      </c>
-      <c r="T117" t="s">
-        <v>55</v>
-      </c>
-      <c r="U117" t="s">
-        <v>56</v>
-      </c>
-      <c r="V117" t="s">
+      <c r="W117" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y117" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z117" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA117" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB117" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC117" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD117" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE117" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH117" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="W117" t="s">
-        <v>58</v>
-      </c>
-      <c r="X117" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y117" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z117" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA117" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB117" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC117" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD117" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE117" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF117" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG117" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH117" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AI117" t="s">
+      <c r="AI117" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ117" t="s">
+      <c r="AJ117" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK117" t="s">
+      <c r="AK117" s="2" t="s">
         <v>68</v>
       </c>
     </row>
